--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N19_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>4.217427722510283</v>
       </c>
       <c r="E2" t="n">
-        <v>21.96419597856077</v>
+        <v>20.72706026494063</v>
       </c>
       <c r="F2" t="n">
-        <v>15.64294779355595</v>
+        <v>15.12140661702667</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>15.36159023114295</v>
       </c>
       <c r="E3" t="n">
-        <v>21.96419597856077</v>
+        <v>20.72706026494063</v>
       </c>
       <c r="F3" t="n">
-        <v>15.64294779355595</v>
+        <v>15.12140661702667</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>45.64561317064855</v>
       </c>
       <c r="E4" t="n">
-        <v>21.96419597856077</v>
+        <v>20.72706026494063</v>
       </c>
       <c r="F4" t="n">
-        <v>15.64294779355595</v>
+        <v>15.12140661702667</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>51.93941806516226</v>
       </c>
       <c r="E5" t="n">
-        <v>21.96419597856077</v>
+        <v>20.72706026494063</v>
       </c>
       <c r="F5" t="n">
-        <v>15.64294779355595</v>
+        <v>15.12140661702667</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>35.00603281996587</v>
       </c>
       <c r="E6" t="n">
-        <v>21.96419597856077</v>
+        <v>20.72706026494063</v>
       </c>
       <c r="F6" t="n">
-        <v>15.64294779355595</v>
+        <v>15.12140661702667</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>19.49968763045604</v>
       </c>
       <c r="E7" t="n">
-        <v>21.96419597856077</v>
+        <v>20.72706026494063</v>
       </c>
       <c r="F7" t="n">
-        <v>15.64294779355595</v>
+        <v>15.12140661702667</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>44.4546488991945</v>
       </c>
       <c r="E8" t="n">
-        <v>21.96419597856077</v>
+        <v>20.72706026494063</v>
       </c>
       <c r="F8" t="n">
-        <v>15.64294779355595</v>
+        <v>15.12140661702667</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>26.93657307816948</v>
       </c>
       <c r="E9" t="n">
-        <v>21.96419597856077</v>
+        <v>20.72706026494063</v>
       </c>
       <c r="F9" t="n">
-        <v>15.64294779355595</v>
+        <v>15.12140661702667</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -721,6 +721,38 @@
         </is>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>W0029F0001T0006Z000C1N19.png</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>43.10269649045056</v>
+      </c>
+      <c r="D10" t="n">
+        <v>41.00501337200946</v>
+      </c>
+      <c r="E10" t="n">
+        <v>20.72706026494063</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15.12140661702667</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.25015279389561</v>
+        <v>0.5281498290080366</v>
       </c>
       <c r="D2" t="n">
-        <v>4.217427722510283</v>
+        <v>0.6853320049079209</v>
       </c>
       <c r="E2" t="n">
-        <v>20.72706026494063</v>
+        <v>3.368147293052853</v>
       </c>
       <c r="F2" t="n">
-        <v>15.12140661702667</v>
+        <v>2.457228575266834</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.04939824813767</v>
+        <v>2.445527215322371</v>
       </c>
       <c r="D3" t="n">
-        <v>15.36159023114295</v>
+        <v>2.496258412560729</v>
       </c>
       <c r="E3" t="n">
-        <v>20.72706026494063</v>
+        <v>3.368147293052853</v>
       </c>
       <c r="F3" t="n">
-        <v>15.12140661702667</v>
+        <v>2.457228575266834</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.02832010455575</v>
+        <v>7.15460201699031</v>
       </c>
       <c r="D4" t="n">
-        <v>45.64561317064855</v>
+        <v>7.41741214023039</v>
       </c>
       <c r="E4" t="n">
-        <v>20.72706026494063</v>
+        <v>3.368147293052853</v>
       </c>
       <c r="F4" t="n">
-        <v>15.12140661702667</v>
+        <v>2.457228575266834</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.88831350335461</v>
+        <v>8.594350944295124</v>
       </c>
       <c r="D5" t="n">
-        <v>51.93941806516226</v>
+        <v>8.440155435588869</v>
       </c>
       <c r="E5" t="n">
-        <v>20.72706026494063</v>
+        <v>3.368147293052853</v>
       </c>
       <c r="F5" t="n">
-        <v>15.12140661702667</v>
+        <v>2.457228575266834</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>66.92695134921753</v>
+        <v>10.87562959424785</v>
       </c>
       <c r="D6" t="n">
-        <v>35.00603281996587</v>
+        <v>5.688480333244454</v>
       </c>
       <c r="E6" t="n">
-        <v>20.72706026494063</v>
+        <v>3.368147293052853</v>
       </c>
       <c r="F6" t="n">
-        <v>15.12140661702667</v>
+        <v>2.457228575266834</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>67.86077681287756</v>
+        <v>11.0273762320926</v>
       </c>
       <c r="D7" t="n">
-        <v>19.49968763045604</v>
+        <v>3.168699239949106</v>
       </c>
       <c r="E7" t="n">
-        <v>20.72706026494063</v>
+        <v>3.368147293052853</v>
       </c>
       <c r="F7" t="n">
-        <v>15.12140661702667</v>
+        <v>2.457228575266834</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.41257124812049</v>
+        <v>7.379542827819579</v>
       </c>
       <c r="D8" t="n">
-        <v>44.4546488991945</v>
+        <v>7.223880446119107</v>
       </c>
       <c r="E8" t="n">
-        <v>20.72706026494063</v>
+        <v>3.368147293052853</v>
       </c>
       <c r="F8" t="n">
-        <v>15.12140661702667</v>
+        <v>2.457228575266834</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.80808869064845</v>
+        <v>4.356314412230374</v>
       </c>
       <c r="D9" t="n">
-        <v>26.93657307816948</v>
+        <v>4.377193125202542</v>
       </c>
       <c r="E9" t="n">
-        <v>20.72706026494063</v>
+        <v>3.368147293052853</v>
       </c>
       <c r="F9" t="n">
-        <v>15.12140661702667</v>
+        <v>2.457228575266834</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.10269649045056</v>
+        <v>7.004188179698216</v>
       </c>
       <c r="D10" t="n">
-        <v>41.00501337200946</v>
+        <v>6.663314672951537</v>
       </c>
       <c r="E10" t="n">
-        <v>20.72706026494063</v>
+        <v>3.368147293052853</v>
       </c>
       <c r="F10" t="n">
-        <v>15.12140661702667</v>
+        <v>2.457228575266834</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
